--- a/artfynd/S 1825-2025 artfynd.xlsx
+++ b/artfynd/S 1825-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,6 +813,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76514344</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -944,6 +954,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76512185</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1080,6 +1095,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76511066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1216,6 +1236,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76511067</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1342,6 +1367,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209454</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1468,6 +1498,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209455</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1594,6 +1629,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209456</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1720,6 +1760,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209457</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1856,6 +1901,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76514789</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1992,6 +2042,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76510625</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2128,6 +2183,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76500006</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2264,6 +2324,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76500007</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2400,6 +2465,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76500008</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2536,6 +2606,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76500009</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2672,6 +2747,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76495156</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2808,6 +2888,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76495157</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2944,6 +3029,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76495158</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3080,6 +3170,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76495160</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3216,6 +3311,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76495161</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3352,6 +3452,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76495162</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3488,6 +3593,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76495163</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3624,6 +3734,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76495164</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3750,6 +3865,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209451</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3876,6 +3996,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209452</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4012,6 +4137,11 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76509939</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4138,8 +4268,41 @@
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131209453</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>